--- a/reports/geoaudit_report.xlsx
+++ b/reports/geoaudit_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,33 @@
         <v>60.71</v>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>MOYEN</t>
         </is>
@@ -523,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +620,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="3">
@@ -626,7 +653,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="4">
@@ -659,7 +686,7 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="5">
@@ -692,7 +719,7 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="6">
@@ -725,7 +752,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="7">
@@ -758,7 +785,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +818,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +851,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="10">
@@ -857,7 +884,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +917,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +950,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="13">
@@ -956,7 +983,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="14">
@@ -989,7 +1016,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="15">
@@ -1022,7 +1049,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="16">
@@ -1055,7 +1082,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="17">
@@ -1088,7 +1115,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46215.63143710565</v>
+        <v>46215.76908900739</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1148,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="19">
@@ -1154,7 +1181,7 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="20">
@@ -1187,7 +1214,7 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="21">
@@ -1220,7 +1247,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="22">
@@ -1253,7 +1280,7 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="23">
@@ -1286,7 +1313,7 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="24">
@@ -1319,7 +1346,7 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="25">
@@ -1352,7 +1379,7 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="26">
@@ -1385,7 +1412,7 @@
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="27">
@@ -1418,7 +1445,7 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="28">
@@ -1451,7 +1478,7 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="29">
@@ -1484,7 +1511,7 @@
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="30">
@@ -1517,7 +1544,7 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="31">
@@ -1550,7 +1577,7 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="32">
@@ -1583,7 +1610,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
       </c>
     </row>
     <row r="33">
@@ -1616,7 +1643,535 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46215.63143905852</v>
+        <v>46215.76909200804</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BOX(2.1655421457014 48.743385629116,2.538242116570473 48.95756799268)</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>46215.7690938201</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>46215.7690938201</v>
       </c>
     </row>
   </sheetData>

--- a/reports/geoaudit_report.xlsx
+++ b/reports/geoaudit_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,23 +461,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>60.71</v>
+        <v>53.57</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -488,52 +488,268 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>60.71</v>
+        <v>32.14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MOYEN</t>
+          <t>CRITIQUE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>28</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>60.71</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CRITIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MOYEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>MOYEN</t>
         </is>
@@ -550,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +819,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -620,7 +836,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="3">
@@ -636,7 +852,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -653,7 +869,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="4">
@@ -669,7 +885,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -678,7 +894,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1287</v>
+        <v>540</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -686,7 +902,7 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="5">
@@ -702,7 +918,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -711,15 +927,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1287</v>
+        <v>540</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>POLYGON</t>
+          <t>POINT</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +951,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -744,7 +960,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1287</v>
+        <v>540</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -752,7 +968,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="7">
@@ -768,7 +984,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -785,7 +1001,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="8">
@@ -801,16 +1017,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -818,7 +1034,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="9">
@@ -834,7 +1050,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -843,7 +1059,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -851,7 +1067,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="10">
@@ -867,7 +1083,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -876,7 +1092,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1287</v>
+        <v>540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -884,7 +1100,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="11">
@@ -900,7 +1116,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,7 +1125,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15923</v>
+        <v>540</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -917,7 +1133,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +1149,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,11 +1162,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BOX(1.447279504766019 48.120541543740536,3.555686958558566 49.2371907073631)</t>
+          <t>BOX(1.667674 48.18306,3.226477 49.128362)</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="13">
@@ -966,7 +1182,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -983,7 +1199,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="14">
@@ -999,7 +1215,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1016,7 +1232,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="15">
@@ -1032,7 +1248,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1049,7 +1265,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="16">
@@ -1065,7 +1281,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1074,7 +1290,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1082,7 +1298,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="17">
@@ -1098,7 +1314,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>communes_dile_de_france_au_01_janvier</t>
+          <t>agenda_jardins_ouverts_2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1115,7 +1331,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46215.76908900739</v>
+        <v>46216.39675622103</v>
       </c>
     </row>
     <row r="18">
@@ -1131,7 +1347,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1148,7 +1364,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="19">
@@ -1164,16 +1380,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>21958</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1181,7 +1397,7 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="20">
@@ -1197,7 +1413,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1206,7 +1422,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>493602</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1214,7 +1430,7 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="21">
@@ -1230,7 +1446,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1239,15 +1455,15 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>515560</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>POLYGON</t>
+          <t>POINT</t>
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="22">
@@ -1263,7 +1479,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1272,7 +1488,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>515560</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1280,7 +1496,7 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="23">
@@ -1296,16 +1512,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>21958</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1313,7 +1529,7 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="24">
@@ -1329,16 +1545,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>83645</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1346,7 +1562,7 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="25">
@@ -1362,7 +1578,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1371,7 +1587,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1379,7 +1595,7 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="26">
@@ -1395,7 +1611,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1404,7 +1620,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>515560</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1412,7 +1628,7 @@
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="27">
@@ -1428,7 +1644,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1437,7 +1653,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>514</v>
+        <v>493602</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1445,7 +1661,7 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="28">
@@ -1461,7 +1677,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1474,11 +1690,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BOX(2.247561180577504 48.91270668647975,2.328449672778644 48.9510880950149)</t>
+          <t>BOX(1.45074 48.12554,3.51862 49.21537)</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="29">
@@ -1494,7 +1710,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1511,7 +1727,7 @@
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="30">
@@ -1527,7 +1743,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1544,7 +1760,7 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="31">
@@ -1560,7 +1776,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1577,7 +1793,7 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="32">
@@ -1593,7 +1809,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1602,7 +1818,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1610,7 +1826,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="33">
@@ -1626,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>iris</t>
+          <t>base_equipement</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1643,7 +1859,7 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46215.76909200804</v>
+        <v>46216.39675815079</v>
       </c>
     </row>
     <row r="34">
@@ -1659,7 +1875,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1676,7 +1892,7 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="35">
@@ -1692,7 +1908,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1709,7 +1925,7 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="36">
@@ -1725,7 +1941,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1734,7 +1950,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1517</v>
+        <v>911</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1742,7 +1958,7 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="37">
@@ -1758,7 +1974,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1767,7 +1983,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1517</v>
+        <v>911</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1775,7 +1991,7 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="38">
@@ -1791,7 +2007,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1800,7 +2016,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1517</v>
+        <v>911</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1808,7 +2024,7 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="39">
@@ -1824,7 +2040,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1841,7 +2057,7 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="40">
@@ -1857,16 +2073,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1874,7 +2090,7 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="41">
@@ -1890,7 +2106,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1899,7 +2115,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1907,7 +2123,7 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="42">
@@ -1923,7 +2139,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1932,7 +2148,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1517</v>
+        <v>911</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1940,7 +2156,7 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="43">
@@ -1956,7 +2172,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1965,7 +2181,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1517</v>
+        <v>911</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1973,7 +2189,7 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="44">
@@ -1989,7 +2205,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2002,11 +2218,11 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BOX(2.1655421457014 48.743385629116,2.538242116570473 48.95756799268)</t>
+          <t>BOX(-1.637585 -22.30015,166.452817 50.69997)</t>
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="45">
@@ -2022,7 +2238,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2039,7 +2255,7 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="46">
@@ -2055,7 +2271,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2072,7 +2288,7 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="47">
@@ -2088,7 +2304,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2105,7 +2321,7 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="48">
@@ -2121,7 +2337,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+          <t>commerces_de_proximite_agrees_ratp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2138,7 +2354,7 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46215.7690938201</v>
+        <v>46216.39686245337</v>
       </c>
     </row>
     <row r="49">
@@ -2154,24 +2370,4248 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>commerces_de_proximite_agrees_ratp</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>46216.39686245337</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1287</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1287</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>POLYGON</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1287</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1287</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>15923</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BOX(1.447279504766019 48.120541543740536,3.555686958558566 49.2371907073631)</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>55</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>communes_dile_de_france_au_01_janvier</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46216.39686394704</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>94</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>94</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>94</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>94</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>94</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BOX(1.537256172857655 48.242845776981746,3.377112195015451 49.155695153994365)</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>connexion_ecologique_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>46216.39686629891</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>19</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>19</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>POLYGON</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>19</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>19</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>514</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BOX(2.247561180577504 48.91270668647975,2.328449672778644 48.9510880950149)</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>106</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>iris</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>46216.39686816943</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>46</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>46</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>46</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>34</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>46</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>46</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>BOX(1.628985 48.184224,3.3680796083248 49.150058)</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>liste_des_jardins_remarquables</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>46216.39686979438</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>22</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>23</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MULTIPOLYGON, POLYGON</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>23</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>8</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>23</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>36100</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>BOX(1.512300816117757 48.159927697093565,3.434483492443775 49.23776792845291)</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>15</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>natura2000_zsc</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>46216.39687278007</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>64</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>64</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>64</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>64</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>64</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>BOX(2.073944928641944 48.712147750016626,2.595865056806167 49.02604601039325)</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G142" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>projets_de_gares_sdrif_e</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>46216.39687447971</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>26605</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>26605</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>26605</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G151" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>7</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G152" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>13</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G153" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>26605</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>26605</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>BOX(1.541833 48.14828359999995,3.3514197 49.16243079998701)</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>stationnement_velo_en_ile_de_france</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vérification de l emprise spatiale</t>
+        </is>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>46216.39687655784</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>GEOMETRY_VALID</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
           <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Nombre de géométries invalides</t>
+        </is>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EMPTY_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Nombre de géométries vides</t>
+        </is>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SRID_CHECK</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Système de coordonnées différent de EPSG:2154</t>
+        </is>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GEOMETRY_TYPE</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ENTITY_COUNT</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Nombre total d entités</t>
+        </is>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NULL_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Entités sans géométrie</t>
+        </is>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>DUPLICATE_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Géométries identiques détectées</t>
+        </is>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>COLUMN_COUNT</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>15</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Nombre de colonnes attributaires</t>
+        </is>
+      </c>
+      <c r="G169" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NULL_ATTRIBUTES</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Nombre de lignes avec valeurs NULL</t>
+        </is>
+      </c>
+      <c r="G170" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>VERTEX_COUNT</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>1517</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Nombre total de sommets</t>
+        </is>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SPATIAL_EXTENT</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>BOX(2.1655421457014 48.743385629116,2.538242116570473 48.95756799268)</t>
+        </is>
+      </c>
+      <c r="G172" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>MULTIPART_GEOMETRY</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Nombre de géométries multiparties</t>
+        </is>
+      </c>
+      <c r="G173" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ZERO_AREA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Polygones avec surface nulle</t>
+        </is>
+      </c>
+      <c r="G174" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ZERO_LENGTH</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Lignes avec longueur nulle</t>
+        </is>
+      </c>
+      <c r="G175" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GEOMETRY_COMPLEXITY</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Nombre maximum de sommets dans une géométrie</t>
+        </is>
+      </c>
+      <c r="G176" s="1" t="n">
+        <v>46216.39687925567</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EMPTY_EXTENT</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>Vérification de l emprise spatiale</t>
         </is>
       </c>
-      <c r="G49" s="1" t="n">
-        <v>46215.7690938201</v>
+      <c r="G177" s="1" t="n">
+        <v>46216.39687925567</v>
       </c>
     </row>
   </sheetData>

--- a/reports/geoaudit_report.xlsx
+++ b/reports/geoaudit_report.xlsx
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="3">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="5">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="6">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="7">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="8">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="9">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="10">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="11">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="12">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="13">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="14">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="15">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="16">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="17">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46216.39675622103</v>
+        <v>46216.41148744745</v>
       </c>
     </row>
     <row r="18">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="19">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="20">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="21">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="22">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="23">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="24">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="25">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="26">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="27">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="28">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="29">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="30">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="31">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="32">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="33">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46216.39675815079</v>
+        <v>46216.41148930043</v>
       </c>
     </row>
     <row r="34">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="35">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="36">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="37">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="38">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="39">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="40">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="41">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="42">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="43">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="44">
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="45">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="46">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="47">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="48">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="49">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46216.39686245337</v>
+        <v>46216.4116167965</v>
       </c>
     </row>
     <row r="50">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="51">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="52">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="53">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="54">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="55">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="56">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="57">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="58">
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="59">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="60">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="61">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="62">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="63">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="64">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="65">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46216.39686394704</v>
+        <v>46216.41161839509</v>
       </c>
     </row>
     <row r="66">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="67">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="68">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="69">
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="70">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="71">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="72">
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="73">
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="74">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="75">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="76">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="77">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="78">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="79">
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="80">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="81">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46216.39686629891</v>
+        <v>46216.41162092915</v>
       </c>
     </row>
     <row r="82">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="83">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="84">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="85">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="86">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="87">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="88">
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="89">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="90">
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="91">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="92">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="93">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="94">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="95">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="96">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="97">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46216.39686816943</v>
+        <v>46216.41162249682</v>
       </c>
     </row>
     <row r="98">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="99">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="100">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="101">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="102">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="103">
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="104">
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="105">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="106">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="107">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="108">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="109">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="110">
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="111">
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="112">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="113">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>46216.39686979438</v>
+        <v>46216.41162407512</v>
       </c>
     </row>
     <row r="114">
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="115">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="116">
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="117">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="118">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="119">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="120">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="121">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="122">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="123">
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="124">
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="125">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="126">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="127">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="128">
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="129">
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>46216.39687278007</v>
+        <v>46216.41162567645</v>
       </c>
     </row>
     <row r="130">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="131">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="132">
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="133">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="134">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="135">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="136">
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="137">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="138">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="139">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="140">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="141">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="142">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="143">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="144">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="145">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>46216.39687447971</v>
+        <v>46216.41162742284</v>
       </c>
     </row>
     <row r="146">
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="147">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="148">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="149">
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="150">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="151">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="152">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="153">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="154">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="155">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="156">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="157">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="158">
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="G158" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="159">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="G159" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="160">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="G160" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="161">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46216.39687655784</v>
+        <v>46216.41162945395</v>
       </c>
     </row>
     <row r="162">
@@ -6116,7 +6116,7 @@
         </is>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="163">
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G163" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="164">
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="G164" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="165">
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="166">
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="G166" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="167">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="G167" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="168">
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="G168" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="169">
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="G169" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="170">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="171">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G171" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="172">
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="173">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="174">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="G174" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="175">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G175" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="176">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
     <row r="177">
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="G177" s="1" t="n">
-        <v>46216.39687925567</v>
+        <v>46216.41163247747</v>
       </c>
     </row>
   </sheetData>

--- a/reports/geoaudit_report.xlsx
+++ b/reports/geoaudit_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,27 +488,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
         <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>32.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CRITIQUE</t>
+          <t>MOYEN</t>
         </is>
       </c>
     </row>
@@ -696,60 +696,6 @@
         <v>60.71</v>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>MOYEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D11" t="n">
-        <v>28</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>53.57</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MOYEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D12" t="n">
-        <v>28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>MOYEN</t>
         </is>
@@ -766,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,7 +782,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="3">
@@ -869,7 +815,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +848,7 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="5">
@@ -935,7 +881,7 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="6">
@@ -968,7 +914,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="7">
@@ -1001,7 +947,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="8">
@@ -1034,7 +980,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="9">
@@ -1067,7 +1013,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="10">
@@ -1100,7 +1046,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="11">
@@ -1133,7 +1079,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="12">
@@ -1166,7 +1112,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="13">
@@ -1199,7 +1145,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="14">
@@ -1232,7 +1178,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="15">
@@ -1265,7 +1211,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="16">
@@ -1298,7 +1244,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="17">
@@ -1331,7 +1277,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46216.41148744745</v>
+        <v>46216.61522897824</v>
       </c>
     </row>
     <row r="18">
@@ -1347,7 +1293,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1364,7 +1310,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="19">
@@ -1380,16 +1326,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21958</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1397,7 +1343,7 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="20">
@@ -1413,16 +1359,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>493602</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1430,7 +1376,7 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="21">
@@ -1446,7 +1392,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1455,7 +1401,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>515560</v>
+        <v>286831</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1463,7 +1409,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="22">
@@ -1479,7 +1425,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1488,7 +1434,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>515560</v>
+        <v>286831</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1496,7 +1442,7 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="23">
@@ -1512,16 +1458,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>21958</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1529,7 +1475,7 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="24">
@@ -1545,7 +1491,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1554,7 +1500,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>83645</v>
+        <v>4184</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1562,7 +1508,7 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="25">
@@ -1578,7 +1524,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1587,7 +1533,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1595,7 +1541,7 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="26">
@@ -1611,7 +1557,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1620,7 +1566,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>515560</v>
+        <v>286831</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1628,7 +1574,7 @@
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="27">
@@ -1644,7 +1590,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1653,7 +1599,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>493602</v>
+        <v>286831</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1661,7 +1607,7 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="28">
@@ -1677,7 +1623,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1690,11 +1636,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BOX(1.45074 48.12554,3.51862 49.21537)</t>
+          <t>BOX(598620.1277744038 6868436.5837209765,669264.795726517 6904953.574338398)</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="29">
@@ -1710,7 +1656,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1727,7 +1673,7 @@
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="30">
@@ -1743,7 +1689,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1760,7 +1706,7 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="31">
@@ -1776,7 +1722,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1793,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="32">
@@ -1809,7 +1755,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1826,7 +1772,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="33">
@@ -1842,7 +1788,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>base_equipement</t>
+          <t>base_adresse_95</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1859,7 +1805,7 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46216.41148930043</v>
+        <v>46216.61523071364</v>
       </c>
     </row>
     <row r="34">
@@ -1892,7 +1838,7 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="35">
@@ -1925,7 +1871,7 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="36">
@@ -1958,7 +1904,7 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="37">
@@ -1991,7 +1937,7 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="38">
@@ -2024,7 +1970,7 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="39">
@@ -2057,7 +2003,7 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="40">
@@ -2090,7 +2036,7 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="41">
@@ -2123,7 +2069,7 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="42">
@@ -2156,7 +2102,7 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="43">
@@ -2189,7 +2135,7 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="44">
@@ -2222,7 +2168,7 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="45">
@@ -2255,7 +2201,7 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="46">
@@ -2288,7 +2234,7 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="47">
@@ -2321,7 +2267,7 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="48">
@@ -2354,7 +2300,7 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="49">
@@ -2387,7 +2333,7 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46216.4116167965</v>
+        <v>46216.61525909854</v>
       </c>
     </row>
     <row r="50">
@@ -2420,7 +2366,7 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="51">
@@ -2453,7 +2399,7 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="52">
@@ -2486,7 +2432,7 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="53">
@@ -2519,7 +2465,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="54">
@@ -2552,7 +2498,7 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="55">
@@ -2585,7 +2531,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="56">
@@ -2618,7 +2564,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="57">
@@ -2651,7 +2597,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="58">
@@ -2684,7 +2630,7 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="59">
@@ -2717,7 +2663,7 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="60">
@@ -2750,7 +2696,7 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="61">
@@ -2783,7 +2729,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="62">
@@ -2816,7 +2762,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="63">
@@ -2849,7 +2795,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="64">
@@ -2882,7 +2828,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="65">
@@ -2915,7 +2861,7 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46216.41161839509</v>
+        <v>46216.6152604887</v>
       </c>
     </row>
     <row r="66">
@@ -2948,7 +2894,7 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="67">
@@ -2981,7 +2927,7 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="68">
@@ -3014,7 +2960,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="69">
@@ -3047,7 +2993,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="70">
@@ -3080,7 +3026,7 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="71">
@@ -3113,7 +3059,7 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="72">
@@ -3146,7 +3092,7 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="73">
@@ -3179,7 +3125,7 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="74">
@@ -3212,7 +3158,7 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="75">
@@ -3245,7 +3191,7 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="76">
@@ -3278,7 +3224,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="77">
@@ -3311,7 +3257,7 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="78">
@@ -3344,7 +3290,7 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="79">
@@ -3377,7 +3323,7 @@
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="80">
@@ -3410,7 +3356,7 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="81">
@@ -3443,7 +3389,7 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46216.41162092915</v>
+        <v>46216.61526172284</v>
       </c>
     </row>
     <row r="82">
@@ -3476,7 +3422,7 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="83">
@@ -3509,7 +3455,7 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="84">
@@ -3542,7 +3488,7 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="85">
@@ -3575,7 +3521,7 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="86">
@@ -3608,7 +3554,7 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="87">
@@ -3641,7 +3587,7 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="88">
@@ -3674,7 +3620,7 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="89">
@@ -3707,7 +3653,7 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="90">
@@ -3740,7 +3686,7 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="91">
@@ -3773,7 +3719,7 @@
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="92">
@@ -3806,7 +3752,7 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="93">
@@ -3839,7 +3785,7 @@
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="94">
@@ -3872,7 +3818,7 @@
         </is>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="95">
@@ -3905,7 +3851,7 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="96">
@@ -3938,7 +3884,7 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="97">
@@ -3971,7 +3917,7 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46216.41162249682</v>
+        <v>46216.61526323869</v>
       </c>
     </row>
     <row r="98">
@@ -4004,7 +3950,7 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="99">
@@ -4037,7 +3983,7 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="100">
@@ -4070,7 +4016,7 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="101">
@@ -4103,7 +4049,7 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="102">
@@ -4136,7 +4082,7 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="103">
@@ -4169,7 +4115,7 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="104">
@@ -4202,7 +4148,7 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="105">
@@ -4235,7 +4181,7 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="106">
@@ -4268,7 +4214,7 @@
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="107">
@@ -4301,7 +4247,7 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="108">
@@ -4334,7 +4280,7 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="109">
@@ -4367,7 +4313,7 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="110">
@@ -4400,7 +4346,7 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="111">
@@ -4433,7 +4379,7 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="112">
@@ -4466,7 +4412,7 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="113">
@@ -4499,7 +4445,7 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>46216.41162407512</v>
+        <v>46216.6152645746</v>
       </c>
     </row>
     <row r="114">
@@ -4532,7 +4478,7 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="115">
@@ -4565,7 +4511,7 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="116">
@@ -4598,7 +4544,7 @@
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="117">
@@ -4631,7 +4577,7 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="118">
@@ -4664,7 +4610,7 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="119">
@@ -4697,7 +4643,7 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="120">
@@ -4730,7 +4676,7 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="121">
@@ -4763,7 +4709,7 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="122">
@@ -4796,7 +4742,7 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="123">
@@ -4829,7 +4775,7 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="124">
@@ -4862,7 +4808,7 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="125">
@@ -4895,7 +4841,7 @@
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="126">
@@ -4928,7 +4874,7 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="127">
@@ -4961,7 +4907,7 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="128">
@@ -4994,7 +4940,7 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="129">
@@ -5027,7 +4973,7 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>46216.41162567645</v>
+        <v>46216.61526605261</v>
       </c>
     </row>
     <row r="130">
@@ -5060,7 +5006,7 @@
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="131">
@@ -5093,7 +5039,7 @@
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="132">
@@ -5126,7 +5072,7 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="133">
@@ -5159,7 +5105,7 @@
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="134">
@@ -5192,7 +5138,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="135">
@@ -5225,7 +5171,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="136">
@@ -5258,7 +5204,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="137">
@@ -5291,7 +5237,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="138">
@@ -5324,7 +5270,7 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="139">
@@ -5357,7 +5303,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="140">
@@ -5390,7 +5336,7 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="141">
@@ -5423,7 +5369,7 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="142">
@@ -5456,7 +5402,7 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="143">
@@ -5489,7 +5435,7 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="144">
@@ -5522,7 +5468,7 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>46216.41162742284</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
     <row r="145">
@@ -5555,1063 +5501,7 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>46216.41162742284</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>G001</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GEOMETRY_VALID</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Nombre de géométries invalides</t>
-        </is>
-      </c>
-      <c r="G146" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>G002</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>EMPTY_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Nombre de géométries vides</t>
-        </is>
-      </c>
-      <c r="G147" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>G003</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SRID_CHECK</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>26605</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Système de coordonnées différent de EPSG:2154</t>
-        </is>
-      </c>
-      <c r="G148" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>G004</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>GEOMETRY_TYPE</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>26605</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>POINT</t>
-        </is>
-      </c>
-      <c r="G149" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>G005</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>ENTITY_COUNT</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>26605</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Nombre total d entités</t>
-        </is>
-      </c>
-      <c r="G150" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>G006</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>NULL_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Entités sans géométrie</t>
-        </is>
-      </c>
-      <c r="G151" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>G007</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>DUPLICATE_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>7</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Géométries identiques détectées</t>
-        </is>
-      </c>
-      <c r="G152" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>G008</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>COLUMN_COUNT</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>13</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Nombre de colonnes attributaires</t>
-        </is>
-      </c>
-      <c r="G153" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>G009</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>NULL_ATTRIBUTES</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>26605</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Nombre de lignes avec valeurs NULL</t>
-        </is>
-      </c>
-      <c r="G154" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>G010</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>VERTEX_COUNT</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>26605</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Nombre total de sommets</t>
-        </is>
-      </c>
-      <c r="G155" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>G011</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>SPATIAL_EXTENT</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>1</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>BOX(1.541833 48.14828359999995,3.3514197 49.16243079998701)</t>
-        </is>
-      </c>
-      <c r="G156" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>G012</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>MULTIPART_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Nombre de géométries multiparties</t>
-        </is>
-      </c>
-      <c r="G157" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>G013</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>ZERO_AREA</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Polygones avec surface nulle</t>
-        </is>
-      </c>
-      <c r="G158" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>G014</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>ZERO_LENGTH</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Lignes avec longueur nulle</t>
-        </is>
-      </c>
-      <c r="G159" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>G015</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>GEOMETRY_COMPLEXITY</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Nombre maximum de sommets dans une géométrie</t>
-        </is>
-      </c>
-      <c r="G160" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>G016</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>EMPTY_EXTENT</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>stationnement_velo_en_ile_de_france</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Vérification de l emprise spatiale</t>
-        </is>
-      </c>
-      <c r="G161" s="1" t="n">
-        <v>46216.41162945395</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>G001</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>GEOMETRY_VALID</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Nombre de géométries invalides</t>
-        </is>
-      </c>
-      <c r="G162" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>G002</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>EMPTY_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Nombre de géométries vides</t>
-        </is>
-      </c>
-      <c r="G163" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>G003</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SRID_CHECK</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>1517</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Système de coordonnées différent de EPSG:2154</t>
-        </is>
-      </c>
-      <c r="G164" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>G004</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>GEOMETRY_TYPE</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>1517</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>POINT</t>
-        </is>
-      </c>
-      <c r="G165" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>G005</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>ENTITY_COUNT</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>1517</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Nombre total d entités</t>
-        </is>
-      </c>
-      <c r="G166" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>G006</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>NULL_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Entités sans géométrie</t>
-        </is>
-      </c>
-      <c r="G167" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>G007</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>DUPLICATE_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Géométries identiques détectées</t>
-        </is>
-      </c>
-      <c r="G168" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>G008</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>COLUMN_COUNT</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>15</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Nombre de colonnes attributaires</t>
-        </is>
-      </c>
-      <c r="G169" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>G009</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>NULL_ATTRIBUTES</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>1517</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Nombre de lignes avec valeurs NULL</t>
-        </is>
-      </c>
-      <c r="G170" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>G010</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>VERTEX_COUNT</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
-        <v>1517</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Nombre total de sommets</t>
-        </is>
-      </c>
-      <c r="G171" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>G011</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SPATIAL_EXTENT</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>BOX(2.1655421457014 48.743385629116,2.538242116570473 48.95756799268)</t>
-        </is>
-      </c>
-      <c r="G172" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>G012</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>MULTIPART_GEOMETRY</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Nombre de géométries multiparties</t>
-        </is>
-      </c>
-      <c r="G173" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>G013</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>ZERO_AREA</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Polygones avec surface nulle</t>
-        </is>
-      </c>
-      <c r="G174" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>G014</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>ZERO_LENGTH</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Lignes avec longueur nulle</t>
-        </is>
-      </c>
-      <c r="G175" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>G015</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>GEOMETRY_COMPLEXITY</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Nombre maximum de sommets dans une géométrie</t>
-        </is>
-      </c>
-      <c r="G176" s="1" t="n">
-        <v>46216.41163247747</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>G016</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>EMPTY_EXTENT</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>velib_velos_et_bornes_disponibilite_temps_reel</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Vérification de l emprise spatiale</t>
-        </is>
-      </c>
-      <c r="G177" s="1" t="n">
-        <v>46216.41163247747</v>
+        <v>46216.61526755332</v>
       </c>
     </row>
   </sheetData>

--- a/reports/geoaudit_report.xlsx
+++ b/reports/geoaudit_report.xlsx
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="3">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="4">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="5">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="6">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="9">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="10">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="11">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="12">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="13">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="14">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="15">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="16">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="17">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46216.61522897824</v>
+        <v>46216.8854951311</v>
       </c>
     </row>
     <row r="18">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="19">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="20">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="21">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="22">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="23">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="24">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="25">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="26">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="27">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="28">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="29">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="30">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="31">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="32">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="33">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46216.61523071364</v>
+        <v>46216.88550481235</v>
       </c>
     </row>
     <row r="34">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="35">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="36">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="37">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="38">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="39">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="40">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="41">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="42">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="43">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="44">
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="45">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="46">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="47">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="48">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="49">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46216.61525909854</v>
+        <v>46216.88554627167</v>
       </c>
     </row>
     <row r="50">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="51">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="52">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="53">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="54">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="55">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="56">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="57">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="58">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="59">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="60">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="61">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="62">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="63">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="64">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="65">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46216.6152604887</v>
+        <v>46216.88554786337</v>
       </c>
     </row>
     <row r="66">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="67">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="68">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="69">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="70">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="71">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="72">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="73">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="74">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="75">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="76">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="77">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="78">
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="79">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="80">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="81">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46216.61526172284</v>
+        <v>46216.88555043993</v>
       </c>
     </row>
     <row r="82">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="83">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="84">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="85">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="86">
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="87">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="88">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="89">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="90">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="91">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="92">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="93">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="94">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="95">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="96">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="97">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46216.61526323869</v>
+        <v>46216.88555203022</v>
       </c>
     </row>
     <row r="98">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="99">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="100">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="101">
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="102">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="103">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="104">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="105">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="106">
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="107">
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="108">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="109">
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="110">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="111">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="112">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="113">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>46216.6152645746</v>
+        <v>46216.88555373036</v>
       </c>
     </row>
     <row r="114">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="115">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="116">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="117">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="118">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="119">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="120">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="121">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="122">
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="123">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="124">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="125">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="126">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="127">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="128">
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="129">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>46216.61526605261</v>
+        <v>46216.88555545675</v>
       </c>
     </row>
     <row r="130">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="131">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="132">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="133">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="134">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="135">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="136">
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="137">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="138">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="139">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="140">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="141">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="142">
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="143">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="144">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
     <row r="145">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>46216.61526755332</v>
+        <v>46216.88555759725</v>
       </c>
     </row>
   </sheetData>
